--- a/data/trans_dic/P21_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P21_R-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado un servicio de urgencias en el último año</t>
+          <t>Población que ha utilizado un servicio de urgencias en el último año (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,49; 20,37</t>
+          <t>13,28; 20,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,68; 16,29</t>
+          <t>9,37; 16,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,38; 18,68</t>
+          <t>11,53; 19,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20,27; 28,65</t>
+          <t>20,48; 29,07</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,22; 27,4</t>
+          <t>17,8; 27,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,01; 31,75</t>
+          <t>20,41; 31,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,08; 26,71</t>
+          <t>18,0; 27,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>20,91; 27,98</t>
+          <t>21,17; 27,96</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,09; 21,57</t>
+          <t>16,11; 21,84</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15,24; 21,15</t>
+          <t>15,44; 21,13</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15,28; 20,96</t>
+          <t>15,56; 21,13</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>21,55; 27,24</t>
+          <t>21,81; 27,22</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,28; 22,92</t>
+          <t>14,05; 23,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,42; 21,13</t>
+          <t>13,39; 21,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,35; 18,79</t>
+          <t>11,11; 18,78</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,97; 21,04</t>
+          <t>13,77; 20,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,98; 29,1</t>
+          <t>20,48; 28,94</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,21; 30,78</t>
+          <t>20,98; 31,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,81; 26,45</t>
+          <t>17,67; 26,53</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>22,33; 30,21</t>
+          <t>22,47; 30,23</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18,46; 24,41</t>
+          <t>18,49; 24,55</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18,01; 24,2</t>
+          <t>17,98; 24,62</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15,73; 21,46</t>
+          <t>15,67; 21,31</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,46; 24,06</t>
+          <t>18,49; 23,63</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,64; 21,21</t>
+          <t>14,57; 20,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21,39; 28,66</t>
+          <t>21,44; 28,96</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,81; 20,93</t>
+          <t>13,92; 20,91</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4,7; 21,72</t>
+          <t>5,04; 22,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21,82; 35,62</t>
+          <t>21,46; 35,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,22; 26,31</t>
+          <t>15,29; 25,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,73; 25,83</t>
+          <t>13,49; 25,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>25,91; 37,86</t>
+          <t>25,99; 38,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,38; 23,18</t>
+          <t>17,33; 23,43</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20,81; 26,68</t>
+          <t>20,78; 26,8</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14,98; 20,82</t>
+          <t>14,88; 20,87</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,57; 25,0</t>
+          <t>6,64; 24,68</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,99; 20,48</t>
+          <t>15,74; 20,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19,8; 24,73</t>
+          <t>19,47; 24,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,37; 18,98</t>
+          <t>14,62; 18,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,15; 24,96</t>
+          <t>19,23; 25,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,89; 29,45</t>
+          <t>23,37; 29,73</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,78; 32,66</t>
+          <t>25,51; 32,31</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,26; 27,16</t>
+          <t>21,22; 27,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>27,44; 71,14</t>
+          <t>27,19; 65,83</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,55; 23,16</t>
+          <t>19,34; 23,03</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22,8; 26,77</t>
+          <t>22,61; 26,77</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18,19; 21,79</t>
+          <t>18,08; 21,66</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>23,85; 51,36</t>
+          <t>23,97; 54,26</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,44; 18,1</t>
+          <t>10,7; 18,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,65; 25,22</t>
+          <t>17,92; 25,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,08; 19,17</t>
+          <t>13,6; 19,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16,9; 24,62</t>
+          <t>17,06; 24,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,8; 28,17</t>
+          <t>20,26; 27,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,41; 33,84</t>
+          <t>27,2; 34,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,71; 23,88</t>
+          <t>17,54; 23,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15,73; 24,64</t>
+          <t>15,7; 24,71</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>17,45; 22,94</t>
+          <t>17,56; 23,12</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24,3; 29,38</t>
+          <t>24,23; 29,49</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16,39; 20,76</t>
+          <t>16,39; 20,87</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,13; 23,29</t>
+          <t>17,32; 23,44</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11,25; 19,37</t>
+          <t>11,4; 19,46</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17,42; 27,89</t>
+          <t>17,78; 28,54</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17,82; 27,53</t>
+          <t>17,7; 27,82</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12,31; 28,9</t>
+          <t>12,05; 30,4</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>21,01; 25,71</t>
+          <t>20,95; 25,88</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,42; 29,94</t>
+          <t>24,33; 29,91</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,0; 23,15</t>
+          <t>17,69; 22,9</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>18,61; 24,38</t>
+          <t>18,47; 23,81</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19,83; 23,94</t>
+          <t>19,77; 23,85</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>24,17; 28,83</t>
+          <t>24,02; 29,04</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>18,41; 22,88</t>
+          <t>18,64; 23,03</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>18,19; 24,04</t>
+          <t>17,96; 24,32</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>15,81; 18,51</t>
+          <t>15,8; 18,41</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>19,33; 22,15</t>
+          <t>19,23; 22,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15,42; 18,07</t>
+          <t>15,44; 18,06</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15,46; 21,66</t>
+          <t>15,41; 21,53</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>22,93; 25,89</t>
+          <t>23,02; 25,98</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,93; 29,04</t>
+          <t>26,15; 29,12</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,09; 22,99</t>
+          <t>20,3; 23,05</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>23,71; 43,85</t>
+          <t>23,72; 42,92</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>19,93; 21,87</t>
+          <t>19,8; 21,82</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23,25; 25,35</t>
+          <t>23,1; 25,28</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18,28; 20,28</t>
+          <t>18,25; 20,19</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>21,13; 33,1</t>
+          <t>21,11; 32,52</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que ha utilizado un servicio de urgencias en el último año</t>
+          <t>Población que ha utilizado un servicio de urgencias en el último año (tasa de respuesta: 99,88%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>63894; 96490</t>
+          <t>62908; 95935</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>42339; 71212</t>
+          <t>40973; 72457</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>48837; 80174</t>
+          <t>49481; 81698</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>102050; 144254</t>
+          <t>103133; 146349</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>55868; 84037</t>
+          <t>54583; 83860</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>66082; 99833</t>
+          <t>64172; 99489</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>62272; 91974</t>
+          <t>61970; 93916</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>93432; 124996</t>
+          <t>94591; 124911</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>125537; 168343</t>
+          <t>125732; 170481</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>114543; 159009</t>
+          <t>116076; 158854</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>118149; 162139</t>
+          <t>120389; 163468</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>204801; 258791</t>
+          <t>207196; 258632</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>52281; 83893</t>
+          <t>51425; 84707</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>56200; 88491</t>
+          <t>56084; 89061</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>42580; 70517</t>
+          <t>41689; 70493</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>63179; 95128</t>
+          <t>62255; 94892</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>74108; 107926</t>
+          <t>75974; 107330</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>71232; 103384</t>
+          <t>70456; 104820</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>66162; 98241</t>
+          <t>65610; 98530</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>85238; 115316</t>
+          <t>85753; 115389</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>136030; 179916</t>
+          <t>136247; 180954</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>135899; 182654</t>
+          <t>135678; 185832</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>117463; 160258</t>
+          <t>117007; 159082</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>153976; 200667</t>
+          <t>154172; 197036</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>79406; 115067</t>
+          <t>79039; 113484</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>134403; 180146</t>
+          <t>134739; 181996</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>72072; 109229</t>
+          <t>72659; 109130</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31394; 145174</t>
+          <t>33696; 147739</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>36605; 59756</t>
+          <t>36014; 60125</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>42205; 68452</t>
+          <t>39783; 66082</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20949; 42492</t>
+          <t>22184; 42330</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>43070; 62949</t>
+          <t>43203; 63181</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>123424; 164595</t>
+          <t>123092; 166410</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>184930; 237079</t>
+          <t>184619; 238132</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>102834; 142902</t>
+          <t>102155; 143238</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>63144; 208660</t>
+          <t>55430; 205984</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>197955; 253659</t>
+          <t>194927; 252576</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>229089; 286145</t>
+          <t>225309; 285158</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>164501; 217333</t>
+          <t>167390; 216964</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>198201; 258311</t>
+          <t>199035; 259995</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>163481; 210389</t>
+          <t>166917; 212377</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>197615; 250363</t>
+          <t>195539; 247695</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>175556; 224310</t>
+          <t>175231; 226825</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>268403; 695838</t>
+          <t>265903; 643840</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>381793; 452256</t>
+          <t>377644; 449696</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>438598; 514974</t>
+          <t>435065; 514960</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>358467; 429444</t>
+          <t>356407; 426942</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>480168; 1033751</t>
+          <t>482565; 1092193</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>36599; 63462</t>
+          <t>37494; 63367</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>90141; 128747</t>
+          <t>91476; 128322</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>80655; 118195</t>
+          <t>83848; 119440</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>80273; 116961</t>
+          <t>81043; 118085</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>118302; 160226</t>
+          <t>115219; 157761</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>208461; 257352</t>
+          <t>206862; 259067</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>130761; 176273</t>
+          <t>129454; 176819</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>131890; 206636</t>
+          <t>131662; 207142</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>160413; 210909</t>
+          <t>161395; 212514</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>308895; 373467</t>
+          <t>307992; 374825</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>222097; 281305</t>
+          <t>222043; 282698</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>224937; 305884</t>
+          <t>227509; 307866</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>33549; 57765</t>
+          <t>34009; 58034</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>46504; 74439</t>
+          <t>47447; 76178</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>51160; 79037</t>
+          <t>50829; 79877</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>29611; 69503</t>
+          <t>28972; 73103</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>262306; 321050</t>
+          <t>261557; 323225</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>270919; 332104</t>
+          <t>269913; 331840</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>194572; 250209</t>
+          <t>191228; 247458</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>141141; 184979</t>
+          <t>140136; 180607</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>306740; 370392</t>
+          <t>305857; 368898</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>332697; 396794</t>
+          <t>330540; 399632</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>251850; 312911</t>
+          <t>255039; 315055</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>181733; 240166</t>
+          <t>179437; 243013</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>516913; 605255</t>
+          <t>516543; 601889</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>660780; 757479</t>
+          <t>657648; 756041</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>520388; 609780</t>
+          <t>521097; 609603</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>521695; 730731</t>
+          <t>519947; 726450</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>774485; 874519</t>
+          <t>777477; 877502</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>919661; 1029957</t>
+          <t>927565; 1032851</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>708126; 810484</t>
+          <t>715706; 812666</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>846380; 1565380</t>
+          <t>846844; 1532269</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1324397; 1453579</t>
+          <t>1315957; 1450120</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1619811; 1765827</t>
+          <t>1609170; 1761056</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1261081; 1399464</t>
+          <t>1259392; 1393235</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1467421; 2298363</t>
+          <t>1466024; 2258019</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P21_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P21_R-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,0%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,28; 20,25</t>
+          <t>13,01; 20,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,37; 16,57</t>
+          <t>9,5; 16,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,53; 19,04</t>
+          <t>11,38; 18,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20,48; 29,07</t>
+          <t>20,31; 28,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,8; 27,34</t>
+          <t>17,68; 27,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,41; 31,64</t>
+          <t>20,46; 31,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,0; 27,27</t>
+          <t>17,69; 26,83</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>21,17; 27,96</t>
+          <t>20,74; 27,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16,11; 21,84</t>
+          <t>15,84; 21,57</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15,44; 21,13</t>
+          <t>15,16; 21,21</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15,56; 21,13</t>
+          <t>15,52; 21,19</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>21,81; 27,22</t>
+          <t>21,5; 26,74</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,14%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>14,05; 23,14</t>
+          <t>14,25; 22,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13,39; 21,27</t>
+          <t>13,43; 21,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11,11; 18,78</t>
+          <t>11,28; 19,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,77; 20,98</t>
+          <t>13,72; 20,93</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,48; 28,94</t>
+          <t>19,95; 29,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,98; 31,21</t>
+          <t>20,68; 30,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,67; 26,53</t>
+          <t>18,21; 27,26</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>22,47; 30,23</t>
+          <t>22,19; 30,11</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>18,49; 24,55</t>
+          <t>18,58; 24,92</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17,98; 24,62</t>
+          <t>17,9; 24,16</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15,67; 21,31</t>
+          <t>15,88; 21,53</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,49; 23,63</t>
+          <t>18,73; 24,04</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>23,63%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>14,57; 20,92</t>
+          <t>14,94; 21,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21,44; 28,96</t>
+          <t>21,31; 28,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,92; 20,91</t>
+          <t>14,12; 20,99</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,04; 22,11</t>
+          <t>16,71; 24,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21,46; 35,84</t>
+          <t>21,01; 34,79</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,29; 25,4</t>
+          <t>15,79; 25,98</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,49; 25,73</t>
+          <t>13,96; 26,07</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>25,99; 38,0</t>
+          <t>25,99; 38,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,33; 23,43</t>
+          <t>17,26; 23,35</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>20,78; 26,8</t>
+          <t>20,88; 26,54</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14,88; 20,87</t>
+          <t>14,76; 20,49</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,64; 24,68</t>
+          <t>20,78; 27,13</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>24,88%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>15,74; 20,4</t>
+          <t>16,02; 20,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19,47; 24,64</t>
+          <t>19,51; 24,53</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,62; 18,95</t>
+          <t>14,53; 19,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,23; 25,12</t>
+          <t>19,59; 25,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,37; 29,73</t>
+          <t>23,45; 29,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,51; 32,31</t>
+          <t>25,6; 32,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,22; 27,46</t>
+          <t>21,51; 27,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>27,19; 65,83</t>
+          <t>25,76; 31,28</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19,34; 23,03</t>
+          <t>19,46; 23,07</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>22,61; 26,77</t>
+          <t>22,79; 26,93</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18,08; 21,66</t>
+          <t>18,17; 21,86</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>23,97; 54,26</t>
+          <t>23,18; 26,93</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>22,08%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>10,7; 18,08</t>
+          <t>10,14; 17,87</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17,92; 25,13</t>
+          <t>18,18; 24,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13,6; 19,37</t>
+          <t>13,44; 19,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17,06; 24,86</t>
+          <t>16,08; 23,31</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,26; 27,74</t>
+          <t>20,2; 27,94</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,2; 34,06</t>
+          <t>26,94; 33,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,54; 23,95</t>
+          <t>17,41; 23,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15,7; 24,71</t>
+          <t>21,75; 26,77</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>17,56; 23,12</t>
+          <t>17,64; 22,95</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24,23; 29,49</t>
+          <t>24,47; 29,58</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16,39; 20,87</t>
+          <t>16,38; 20,88</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>17,32; 23,44</t>
+          <t>20,17; 24,29</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,17%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11,4; 19,46</t>
+          <t>10,83; 19,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17,78; 28,54</t>
+          <t>17,73; 27,6</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17,7; 27,82</t>
+          <t>16,94; 27,35</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12,05; 30,4</t>
+          <t>11,3; 26,74</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>20,95; 25,88</t>
+          <t>20,99; 25,66</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>24,33; 29,91</t>
+          <t>24,66; 30,34</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17,69; 22,9</t>
+          <t>17,91; 22,69</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>18,47; 23,81</t>
+          <t>18,38; 23,68</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>19,77; 23,85</t>
+          <t>19,7; 23,75</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>24,02; 29,04</t>
+          <t>23,88; 28,77</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>18,64; 23,03</t>
+          <t>18,43; 23,16</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>17,96; 24,32</t>
+          <t>17,42; 23,05</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>22,88%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>15,8; 18,41</t>
+          <t>15,84; 18,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>19,23; 22,11</t>
+          <t>19,27; 22,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15,44; 18,06</t>
+          <t>15,46; 18,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15,41; 21,53</t>
+          <t>19,23; 22,24</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>23,02; 25,98</t>
+          <t>22,91; 25,75</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>26,15; 29,12</t>
+          <t>26,12; 29,18</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>20,3; 23,05</t>
+          <t>20,17; 23,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>23,72; 42,92</t>
+          <t>23,71; 26,28</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>19,8; 21,82</t>
+          <t>19,81; 21,85</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23,1; 25,28</t>
+          <t>23,24; 25,26</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18,25; 20,19</t>
+          <t>18,27; 20,26</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>21,11; 32,52</t>
+          <t>21,95; 23,95</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>121437</t>
+          <t>130751</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>109067</t>
+          <t>117961</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>230503</t>
+          <t>248712</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>62908; 95935</t>
+          <t>61646; 96379</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>40973; 72457</t>
+          <t>41529; 70829</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>49481; 81698</t>
+          <t>48823; 80490</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>103133; 146349</t>
+          <t>111448; 154512</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>54583; 83860</t>
+          <t>54230; 83837</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>64172; 99489</t>
+          <t>64337; 98853</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>61970; 93916</t>
+          <t>60907; 92396</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>94591; 124911</t>
+          <t>101126; 133554</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>125732; 170481</t>
+          <t>123627; 168315</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>116076; 158854</t>
+          <t>113987; 159433</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>120389; 163468</t>
+          <t>120015; 163869</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>207196; 258632</t>
+          <t>222850; 277152</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>77533</t>
+          <t>82222</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>98799</t>
+          <t>109159</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>176332</t>
+          <t>191382</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>51425; 84707</t>
+          <t>52165; 82680</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>56084; 89061</t>
+          <t>56261; 89106</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>41689; 70493</t>
+          <t>42317; 71704</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>62255; 94892</t>
+          <t>66289; 101125</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>75974; 107330</t>
+          <t>73989; 107856</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>70456; 104820</t>
+          <t>69464; 103714</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>65610; 98530</t>
+          <t>67640; 101248</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>85753; 115389</t>
+          <t>93720; 127166</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>136247; 180954</t>
+          <t>136950; 183654</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>135678; 185832</t>
+          <t>135120; 182329</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>117007; 159082</t>
+          <t>118601; 160764</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>154172; 197036</t>
+          <t>169574; 217656</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>87537</t>
+          <t>96727</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>52277</t>
+          <t>58832</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>139814</t>
+          <t>155558</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>79039; 113484</t>
+          <t>81051; 115214</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>134739; 181996</t>
+          <t>133950; 180351</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>72659; 109130</t>
+          <t>73717; 109561</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33696; 147739</t>
+          <t>78791; 116575</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>36014; 60125</t>
+          <t>35248; 58370</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>39783; 66082</t>
+          <t>41070; 67573</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22184; 42330</t>
+          <t>22971; 42892</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>43203; 63181</t>
+          <t>48548; 71194</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>123092; 166410</t>
+          <t>122565; 165860</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>184619; 238132</t>
+          <t>185522; 235820</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>102155; 143238</t>
+          <t>101342; 140636</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>55430; 205984</t>
+          <t>136797; 178600</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>226630</t>
+          <t>250508</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>422536</t>
+          <t>245298</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>649166</t>
+          <t>495806</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>194927; 252576</t>
+          <t>198359; 253591</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>225309; 285158</t>
+          <t>225734; 283899</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>167390; 216964</t>
+          <t>166320; 218564</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>199035; 259995</t>
+          <t>221692; 283345</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>166917; 212377</t>
+          <t>167479; 212881</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>195539; 247695</t>
+          <t>196241; 245535</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>175231; 226825</t>
+          <t>177652; 227911</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>265903; 643840</t>
+          <t>221888; 269360</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>377644; 449696</t>
+          <t>379988; 450543</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>435065; 514960</t>
+          <t>438534; 518097</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>356407; 426942</t>
+          <t>358028; 430932</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>482565; 1092193</t>
+          <t>462000; 536734</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>96544</t>
+          <t>109341</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>177207</t>
+          <t>199245</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>273751</t>
+          <t>308586</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>37494; 63367</t>
+          <t>35538; 62653</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>91476; 128322</t>
+          <t>92840; 127345</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>83848; 119440</t>
+          <t>82850; 121073</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>81043; 118085</t>
+          <t>91337; 132390</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>115219; 157761</t>
+          <t>114869; 158899</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>206862; 259067</t>
+          <t>204909; 258423</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>129454; 176819</t>
+          <t>128499; 173576</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>131662; 207142</t>
+          <t>180457; 222120</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>161395; 212514</t>
+          <t>162194; 210936</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>307992; 374825</t>
+          <t>311029; 375970</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>222043; 282698</t>
+          <t>221913; 282818</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>227509; 307866</t>
+          <t>281830; 339469</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>46063</t>
+          <t>42377</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>160892</t>
+          <t>175211</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>206955</t>
+          <t>217589</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>34009; 58034</t>
+          <t>32283; 57632</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>47447; 76178</t>
+          <t>47329; 73663</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>50829; 79877</t>
+          <t>48635; 78531</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>28972; 73103</t>
+          <t>26810; 63427</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>261557; 323225</t>
+          <t>262066; 320459</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>269913; 331840</t>
+          <t>273543; 336623</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>191228; 247458</t>
+          <t>193576; 245259</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>140136; 180607</t>
+          <t>154652; 199223</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>305857; 368898</t>
+          <t>304824; 367358</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>330540; 399632</t>
+          <t>328591; 395883</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>255039; 315055</t>
+          <t>252069; 316785</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>179437; 243013</t>
+          <t>187955; 248650</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>655743</t>
+          <t>711926</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>1020778</t>
+          <t>905707</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1676522</t>
+          <t>1617633</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>516543; 601889</t>
+          <t>517748; 600711</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>657648; 756041</t>
+          <t>658747; 757603</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>521097; 609603</t>
+          <t>521939; 610208</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>519947; 726450</t>
+          <t>661699; 765084</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>777477; 877502</t>
+          <t>773754; 869712</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>927565; 1032851</t>
+          <t>926457; 1035071</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>715706; 812666</t>
+          <t>710985; 814941</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>846844; 1532269</t>
+          <t>860473; 953746</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1315957; 1450120</t>
+          <t>1316353; 1452249</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1609170; 1761056</t>
+          <t>1619180; 1760012</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1259392; 1393235</t>
+          <t>1260983; 1398261</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1466024; 2258019</t>
+          <t>1551853; 1693385</t>
         </is>
       </c>
     </row>
